--- a/demo/image_metadata_with_llava_long.xlsx
+++ b/demo/image_metadata_with_llava_long.xlsx
@@ -520,10 +520,10 @@
         <v>3.09</v>
       </c>
       <c r="G3" t="n">
-        <v>0.125</v>
+        <v>12.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.125</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="4">
@@ -554,10 +554,10 @@
         <v>5.13</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1935</v>
+        <v>19.3548</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1935</v>
+        <v>19.3548</v>
       </c>
     </row>
     <row r="5">
@@ -588,10 +588,10 @@
         <v>1.68</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1408</v>
+        <v>14.0845</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1127</v>
+        <v>11.2676</v>
       </c>
     </row>
     <row r="6">
@@ -622,10 +622,10 @@
         <v>1.6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1905</v>
+        <v>19.0476</v>
       </c>
       <c r="H6" t="n">
-        <v>0.127</v>
+        <v>12.6984</v>
       </c>
     </row>
     <row r="7">
@@ -656,10 +656,10 @@
         <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1728</v>
+        <v>17.284</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1481</v>
+        <v>14.8148</v>
       </c>
     </row>
     <row r="8">
@@ -724,10 +724,10 @@
         <v>5.11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1875</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="10">
@@ -758,10 +758,10 @@
         <v>2.17</v>
       </c>
       <c r="G10" t="n">
-        <v>0.24</v>
+        <v>24</v>
       </c>
       <c r="H10" t="n">
-        <v>0.16</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -792,10 +792,10 @@
         <v>2.44</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -826,10 +826,10 @@
         <v>3.51</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2692</v>
+        <v>26.9231</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1538</v>
+        <v>15.3846</v>
       </c>
     </row>
     <row r="13">
@@ -860,10 +860,10 @@
         <v>3.18</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2373</v>
+        <v>23.7288</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2034</v>
+        <v>20.339</v>
       </c>
     </row>
     <row r="14">
@@ -894,10 +894,10 @@
         <v>1.87</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1429</v>
+        <v>14.2857</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07140000000000001</v>
+        <v>7.1429</v>
       </c>
     </row>
     <row r="15">
@@ -928,10 +928,10 @@
         <v>3.36</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3333</v>
+        <v>33.3333</v>
       </c>
       <c r="H15" t="n">
-        <v>0.25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -962,10 +962,10 @@
         <v>5.82</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2759</v>
+        <v>27.5862</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2069</v>
+        <v>20.6897</v>
       </c>
     </row>
     <row r="17">
@@ -996,10 +996,10 @@
         <v>4.75</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2857</v>
+        <v>28.5714</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2857</v>
+        <v>28.5714</v>
       </c>
     </row>
     <row r="18">
@@ -1030,10 +1030,10 @@
         <v>1.31</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1224</v>
+        <v>12.2449</v>
       </c>
       <c r="H18" t="n">
-        <v>0.08160000000000001</v>
+        <v>8.1633</v>
       </c>
     </row>
     <row r="19">
@@ -1064,10 +1064,10 @@
         <v>1.69</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1505</v>
+        <v>15.0538</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1505</v>
+        <v>15.0538</v>
       </c>
     </row>
     <row r="20">
@@ -1132,10 +1132,10 @@
         <v>5.4</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2857</v>
+        <v>28.5714</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2857</v>
+        <v>28.5714</v>
       </c>
     </row>
     <row r="22">
@@ -1166,10 +1166,10 @@
         <v>16.94</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3571</v>
+        <v>35.7143</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3571</v>
+        <v>35.7143</v>
       </c>
     </row>
     <row r="23">
@@ -1200,10 +1200,10 @@
         <v>3.92</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1905</v>
+        <v>19.0476</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1429</v>
+        <v>14.2857</v>
       </c>
     </row>
     <row r="24">
@@ -1234,10 +1234,10 @@
         <v>4.49</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3429</v>
+        <v>34.2857</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3429</v>
+        <v>34.2857</v>
       </c>
     </row>
     <row r="25">
@@ -1268,10 +1268,10 @@
         <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1302,10 +1302,10 @@
         <v>3.99</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4638</v>
+        <v>46.3768</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3188</v>
+        <v>31.8841</v>
       </c>
     </row>
     <row r="27">
@@ -1336,10 +1336,10 @@
         <v>1.82</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0741</v>
+        <v>7.4074</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0741</v>
+        <v>7.4074</v>
       </c>
     </row>
     <row r="28">
@@ -1370,10 +1370,10 @@
         <v>0.85</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0984</v>
+        <v>9.8361</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0984</v>
+        <v>9.8361</v>
       </c>
     </row>
     <row r="29">
@@ -1404,10 +1404,10 @@
         <v>0.82</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1449</v>
+        <v>14.4928</v>
       </c>
       <c r="H29" t="n">
-        <v>0.08699999999999999</v>
+        <v>8.6957</v>
       </c>
     </row>
     <row r="30">
@@ -1438,10 +1438,10 @@
         <v>3.67</v>
       </c>
       <c r="G30" t="n">
-        <v>0.08699999999999999</v>
+        <v>8.6957</v>
       </c>
       <c r="H30" t="n">
-        <v>0.08699999999999999</v>
+        <v>8.6957</v>
       </c>
     </row>
     <row r="31">
@@ -1472,10 +1472,10 @@
         <v>2.02</v>
       </c>
       <c r="G31" t="n">
-        <v>0.241</v>
+        <v>24.0964</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1928</v>
+        <v>19.2771</v>
       </c>
     </row>
     <row r="32">
@@ -1506,10 +1506,10 @@
         <v>1.77</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1846</v>
+        <v>18.4615</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1538</v>
+        <v>15.3846</v>
       </c>
     </row>
     <row r="33">
@@ -1540,10 +1540,10 @@
         <v>3.04</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2069</v>
+        <v>20.6897</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2069</v>
+        <v>20.6897</v>
       </c>
     </row>
     <row r="34">
@@ -1574,10 +1574,10 @@
         <v>1.53</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1026</v>
+        <v>10.2564</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0513</v>
+        <v>5.1282</v>
       </c>
     </row>
     <row r="35">
@@ -1608,10 +1608,10 @@
         <v>0.88</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1111</v>
+        <v>11.1111</v>
       </c>
     </row>
     <row r="36">
@@ -1642,10 +1642,10 @@
         <v>5.06</v>
       </c>
       <c r="G36" t="n">
-        <v>0.08699999999999999</v>
+        <v>8.6957</v>
       </c>
       <c r="H36" t="n">
-        <v>0.08699999999999999</v>
+        <v>8.6957</v>
       </c>
     </row>
     <row r="37">
@@ -1676,10 +1676,10 @@
         <v>6.32</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2857</v>
+        <v>28.5714</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2857</v>
+        <v>28.5714</v>
       </c>
     </row>
     <row r="38">
@@ -1710,10 +1710,10 @@
         <v>5.24</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2353</v>
+        <v>23.5294</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2353</v>
+        <v>23.5294</v>
       </c>
     </row>
     <row r="39">
@@ -1744,10 +1744,10 @@
         <v>3.64</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2979</v>
+        <v>29.7872</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1702</v>
+        <v>17.0213</v>
       </c>
     </row>
     <row r="40">
@@ -1778,10 +1778,10 @@
         <v>1.65</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1333</v>
+        <v>13.3333</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1333</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="41">
@@ -1812,10 +1812,10 @@
         <v>3.33</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -1846,10 +1846,10 @@
         <v>2.17</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2778</v>
+        <v>27.7778</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1944</v>
+        <v>19.4444</v>
       </c>
     </row>
     <row r="43">
@@ -1880,10 +1880,10 @@
         <v>1.69</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1176</v>
+        <v>11.7647</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1176</v>
+        <v>11.7647</v>
       </c>
     </row>
     <row r="44">
@@ -1914,10 +1914,10 @@
         <v>0.54</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0506</v>
+        <v>5.0633</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0506</v>
+        <v>5.0633</v>
       </c>
     </row>
     <row r="45">
@@ -1948,10 +1948,10 @@
         <v>1.05</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0588</v>
+        <v>5.8824</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0588</v>
+        <v>5.8824</v>
       </c>
     </row>
     <row r="46">
@@ -1982,10 +1982,10 @@
         <v>1.34</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1111</v>
+        <v>11.1111</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0556</v>
+        <v>5.5556</v>
       </c>
     </row>
     <row r="47">
@@ -2016,10 +2016,10 @@
         <v>1.7</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="H47" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -2050,10 +2050,10 @@
         <v>0.86</v>
       </c>
       <c r="G48" t="n">
-        <v>0.029</v>
+        <v>2.8986</v>
       </c>
       <c r="H48" t="n">
-        <v>0.029</v>
+        <v>2.8986</v>
       </c>
     </row>
     <row r="49">
@@ -2084,10 +2084,10 @@
         <v>1.98</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -2118,10 +2118,10 @@
         <v>1.04</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0833</v>
+        <v>8.333299999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0833</v>
+        <v>8.333299999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2152,10 +2152,10 @@
         <v>1.16</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1212</v>
+        <v>12.1212</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0606</v>
+        <v>6.0606</v>
       </c>
     </row>
     <row r="52">
@@ -2186,10 +2186,10 @@
         <v>3.65</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1667</v>
+        <v>16.6667</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1667</v>
+        <v>16.6667</v>
       </c>
     </row>
     <row r="53">
@@ -2220,10 +2220,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>0.05</v>
+        <v>5</v>
       </c>
       <c r="H53" t="n">
-        <v>0.05</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -2254,10 +2254,10 @@
         <v>1.45</v>
       </c>
       <c r="G54" t="n">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1562</v>
+        <v>15.625</v>
       </c>
     </row>
     <row r="55">
@@ -2288,10 +2288,10 @@
         <v>2.09</v>
       </c>
       <c r="G55" t="n">
-        <v>0.3077</v>
+        <v>30.7692</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2051</v>
+        <v>20.5128</v>
       </c>
     </row>
     <row r="56">
@@ -2322,10 +2322,10 @@
         <v>30.21</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6</v>
+        <v>60</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57">
@@ -2356,10 +2356,10 @@
         <v>2.72</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -2390,10 +2390,10 @@
         <v>2.27</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2899</v>
+        <v>28.9855</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2029</v>
+        <v>20.2899</v>
       </c>
     </row>
     <row r="59">
@@ -2424,10 +2424,10 @@
         <v>5.4</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3333</v>
+        <v>33.3333</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
@@ -2458,10 +2458,10 @@
         <v>3.16</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3077</v>
+        <v>30.7692</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1538</v>
+        <v>15.3846</v>
       </c>
     </row>
     <row r="61">
@@ -2492,10 +2492,10 @@
         <v>0.55</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0312</v>
+        <v>3.125</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0312</v>
+        <v>3.125</v>
       </c>
     </row>
     <row r="62">
@@ -2560,10 +2560,10 @@
         <v>1.09</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0556</v>
+        <v>5.5556</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0556</v>
+        <v>5.5556</v>
       </c>
     </row>
     <row r="64">
@@ -2594,10 +2594,10 @@
         <v>2.92</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0769</v>
+        <v>7.6923</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0769</v>
+        <v>7.6923</v>
       </c>
     </row>
     <row r="65">
@@ -2628,10 +2628,10 @@
         <v>2.29</v>
       </c>
       <c r="G65" t="n">
-        <v>0.06900000000000001</v>
+        <v>6.8966</v>
       </c>
       <c r="H65" t="n">
-        <v>0.06900000000000001</v>
+        <v>6.8966</v>
       </c>
     </row>
     <row r="66">
@@ -2730,10 +2730,10 @@
         <v>2.92</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0741</v>
+        <v>7.4074</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0741</v>
+        <v>7.4074</v>
       </c>
     </row>
     <row r="69">
@@ -2764,10 +2764,10 @@
         <v>0.92</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0488</v>
+        <v>4.878</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0488</v>
+        <v>4.878</v>
       </c>
     </row>
     <row r="70">
@@ -2866,10 +2866,10 @@
         <v>3.03</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3333</v>
+        <v>33.3333</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73">
@@ -2900,10 +2900,10 @@
         <v>1.19</v>
       </c>
       <c r="G73" t="n">
-        <v>0.16</v>
+        <v>16</v>
       </c>
       <c r="H73" t="n">
-        <v>0.12</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -2934,10 +2934,10 @@
         <v>1.4</v>
       </c>
       <c r="G74" t="n">
-        <v>0.1111</v>
+        <v>11.1111</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1111</v>
+        <v>11.1111</v>
       </c>
     </row>
     <row r="75">
@@ -2968,10 +2968,10 @@
         <v>2.15</v>
       </c>
       <c r="G75" t="n">
-        <v>0.08699999999999999</v>
+        <v>8.6957</v>
       </c>
       <c r="H75" t="n">
-        <v>0.08699999999999999</v>
+        <v>8.6957</v>
       </c>
     </row>
     <row r="76">
@@ -3002,10 +3002,10 @@
         <v>4.05</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0667</v>
+        <v>6.6667</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0667</v>
+        <v>6.6667</v>
       </c>
     </row>
     <row r="77">
@@ -3036,10 +3036,10 @@
         <v>1.34</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1765</v>
+        <v>17.6471</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1765</v>
+        <v>17.6471</v>
       </c>
     </row>
     <row r="78">
@@ -3070,10 +3070,10 @@
         <v>2.15</v>
       </c>
       <c r="G78" t="n">
-        <v>0.06900000000000001</v>
+        <v>6.8966</v>
       </c>
       <c r="H78" t="n">
-        <v>0.06900000000000001</v>
+        <v>6.8966</v>
       </c>
     </row>
     <row r="79">
@@ -3104,10 +3104,10 @@
         <v>0.74</v>
       </c>
       <c r="G79" t="n">
-        <v>0.1143</v>
+        <v>11.4286</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0857</v>
+        <v>8.571400000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3138,10 +3138,10 @@
         <v>0.86</v>
       </c>
       <c r="G80" t="n">
-        <v>0.1449</v>
+        <v>14.4928</v>
       </c>
       <c r="H80" t="n">
-        <v>0.08699999999999999</v>
+        <v>8.6957</v>
       </c>
     </row>
     <row r="81">
@@ -3172,10 +3172,10 @@
         <v>1.65</v>
       </c>
       <c r="G81" t="n">
-        <v>0.16</v>
+        <v>16</v>
       </c>
       <c r="H81" t="n">
-        <v>0.16</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82">
@@ -3206,10 +3206,10 @@
         <v>2.66</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1333</v>
+        <v>13.3333</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0667</v>
+        <v>6.6667</v>
       </c>
     </row>
     <row r="83">
@@ -3240,10 +3240,10 @@
         <v>2.02</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0833</v>
+        <v>8.333299999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0833</v>
+        <v>8.333299999999999</v>
       </c>
     </row>
     <row r="84">
@@ -3274,10 +3274,10 @@
         <v>5.34</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1739</v>
+        <v>17.3913</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1739</v>
+        <v>17.3913</v>
       </c>
     </row>
     <row r="85">
@@ -3308,10 +3308,10 @@
         <v>5.33</v>
       </c>
       <c r="G85" t="n">
-        <v>0.3429</v>
+        <v>34.2857</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2286</v>
+        <v>22.8571</v>
       </c>
     </row>
     <row r="86">
@@ -3342,10 +3342,10 @@
         <v>0.67</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0769</v>
+        <v>7.6923</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0769</v>
+        <v>7.6923</v>
       </c>
     </row>
     <row r="87">
@@ -3376,10 +3376,10 @@
         <v>3.63</v>
       </c>
       <c r="G87" t="n">
-        <v>0.2609</v>
+        <v>26.087</v>
       </c>
       <c r="H87" t="n">
-        <v>0.2174</v>
+        <v>21.7391</v>
       </c>
     </row>
     <row r="88">
@@ -3410,10 +3410,10 @@
         <v>1.79</v>
       </c>
       <c r="G88" t="n">
-        <v>0.1111</v>
+        <v>11.1111</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1111</v>
+        <v>11.1111</v>
       </c>
     </row>
     <row r="89">
@@ -3512,10 +3512,10 @@
         <v>0.96</v>
       </c>
       <c r="G91" t="n">
-        <v>0.1132</v>
+        <v>11.3208</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0755</v>
+        <v>7.5472</v>
       </c>
     </row>
     <row r="92">
@@ -3546,10 +3546,10 @@
         <v>1.43</v>
       </c>
       <c r="G92" t="n">
-        <v>0.1463</v>
+        <v>14.6341</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1463</v>
+        <v>14.6341</v>
       </c>
     </row>
     <row r="93">
@@ -3580,10 +3580,10 @@
         <v>1.98</v>
       </c>
       <c r="G93" t="n">
-        <v>0.129</v>
+        <v>12.9032</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0968</v>
+        <v>9.6774</v>
       </c>
     </row>
     <row r="94">
@@ -3614,10 +3614,10 @@
         <v>1.86</v>
       </c>
       <c r="G94" t="n">
-        <v>0.186</v>
+        <v>18.6047</v>
       </c>
       <c r="H94" t="n">
-        <v>0.093</v>
+        <v>9.302300000000001</v>
       </c>
     </row>
     <row r="95">
@@ -3648,10 +3648,10 @@
         <v>0.61</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0674</v>
+        <v>6.7416</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0674</v>
+        <v>6.7416</v>
       </c>
     </row>
     <row r="96">
@@ -3682,10 +3682,10 @@
         <v>0.96</v>
       </c>
       <c r="G96" t="n">
-        <v>0.1515</v>
+        <v>15.1515</v>
       </c>
       <c r="H96" t="n">
-        <v>0.09089999999999999</v>
+        <v>9.0909</v>
       </c>
     </row>
     <row r="97">
@@ -3716,10 +3716,10 @@
         <v>2.19</v>
       </c>
       <c r="G97" t="n">
-        <v>0.2667</v>
+        <v>26.6667</v>
       </c>
       <c r="H97" t="n">
-        <v>0.16</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98">
@@ -3750,10 +3750,10 @@
         <v>2.1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.2041</v>
+        <v>20.4082</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1224</v>
+        <v>12.2449</v>
       </c>
     </row>
     <row r="99">
@@ -3784,10 +3784,10 @@
         <v>1.57</v>
       </c>
       <c r="G99" t="n">
-        <v>0.1695</v>
+        <v>16.9492</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1356</v>
+        <v>13.5593</v>
       </c>
     </row>
     <row r="100">
@@ -3818,10 +3818,10 @@
         <v>1.17</v>
       </c>
       <c r="G100" t="n">
-        <v>0.1224</v>
+        <v>12.2449</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1224</v>
+        <v>12.2449</v>
       </c>
     </row>
     <row r="101">
@@ -3852,10 +3852,10 @@
         <v>1.72</v>
       </c>
       <c r="G101" t="n">
-        <v>0.2424</v>
+        <v>24.2424</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1212</v>
+        <v>12.1212</v>
       </c>
     </row>
     <row r="102">
@@ -3886,10 +3886,10 @@
         <v>0.86</v>
       </c>
       <c r="G102" t="n">
-        <v>0.1017</v>
+        <v>10.1695</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0678</v>
+        <v>6.7797</v>
       </c>
     </row>
     <row r="103">
@@ -3920,10 +3920,10 @@
         <v>1.17</v>
       </c>
       <c r="G103" t="n">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1136</v>
+        <v>11.3636</v>
       </c>
     </row>
     <row r="104">
@@ -3954,10 +3954,10 @@
         <v>0.12</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0408</v>
+        <v>4.0816</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0408</v>
+        <v>4.0816</v>
       </c>
     </row>
     <row r="105">
@@ -3988,10 +3988,10 @@
         <v>2.53</v>
       </c>
       <c r="G105" t="n">
-        <v>0.2462</v>
+        <v>24.6154</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1231</v>
+        <v>12.3077</v>
       </c>
     </row>
     <row r="106">
@@ -4022,10 +4022,10 @@
         <v>2.03</v>
       </c>
       <c r="G106" t="n">
-        <v>0.1875</v>
+        <v>18.75</v>
       </c>
       <c r="H106" t="n">
-        <v>0.125</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="107">
@@ -4056,10 +4056,10 @@
         <v>2.27</v>
       </c>
       <c r="G107" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="H107" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108">
@@ -4090,10 +4090,10 @@
         <v>1.6</v>
       </c>
       <c r="G108" t="n">
-        <v>0.2553</v>
+        <v>25.5319</v>
       </c>
       <c r="H108" t="n">
-        <v>0.2128</v>
+        <v>21.2766</v>
       </c>
     </row>
     <row r="109">
@@ -4124,10 +4124,10 @@
         <v>1.52</v>
       </c>
       <c r="G109" t="n">
-        <v>0.1579</v>
+        <v>15.7895</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1579</v>
+        <v>15.7895</v>
       </c>
     </row>
     <row r="110">
@@ -4158,10 +4158,10 @@
         <v>1.55</v>
       </c>
       <c r="G110" t="n">
-        <v>0.16</v>
+        <v>16</v>
       </c>
       <c r="H110" t="n">
-        <v>0.12</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111">
@@ -4192,10 +4192,10 @@
         <v>3.55</v>
       </c>
       <c r="G111" t="n">
-        <v>0.2258</v>
+        <v>22.5806</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1935</v>
+        <v>19.3548</v>
       </c>
     </row>
     <row r="112">
@@ -4226,10 +4226,10 @@
         <v>2.52</v>
       </c>
       <c r="G112" t="n">
-        <v>0.125</v>
+        <v>12.5</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0625</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="113">
@@ -4260,10 +4260,10 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G113" t="n">
-        <v>0.2941</v>
+        <v>29.4118</v>
       </c>
       <c r="H113" t="n">
-        <v>0.2941</v>
+        <v>29.4118</v>
       </c>
     </row>
     <row r="114">
@@ -4294,10 +4294,10 @@
         <v>2.61</v>
       </c>
       <c r="G114" t="n">
-        <v>0.1687</v>
+        <v>16.8675</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1446</v>
+        <v>14.4578</v>
       </c>
     </row>
     <row r="115">
@@ -4328,10 +4328,10 @@
         <v>0.66</v>
       </c>
       <c r="G115" t="n">
-        <v>0.102</v>
+        <v>10.2041</v>
       </c>
       <c r="H115" t="n">
-        <v>0.08160000000000001</v>
+        <v>8.1633</v>
       </c>
     </row>
     <row r="116">
@@ -4362,10 +4362,10 @@
         <v>1.51</v>
       </c>
       <c r="G116" t="n">
-        <v>0.1212</v>
+        <v>12.1212</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0606</v>
+        <v>6.0606</v>
       </c>
     </row>
     <row r="117">
@@ -4396,10 +4396,10 @@
         <v>11.69</v>
       </c>
       <c r="G117" t="n">
-        <v>0.3333</v>
+        <v>33.3333</v>
       </c>
       <c r="H117" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
     </row>
     <row r="118">
@@ -4430,10 +4430,10 @@
         <v>1.64</v>
       </c>
       <c r="G118" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1333</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="119">
@@ -4464,10 +4464,10 @@
         <v>0.33</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0588</v>
+        <v>5.8824</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0588</v>
+        <v>5.8824</v>
       </c>
     </row>
     <row r="120">
@@ -4498,10 +4498,10 @@
         <v>0.92</v>
       </c>
       <c r="G120" t="n">
-        <v>0.1515</v>
+        <v>15.1515</v>
       </c>
       <c r="H120" t="n">
-        <v>0.09089999999999999</v>
+        <v>9.0909</v>
       </c>
     </row>
     <row r="121">
@@ -4532,10 +4532,10 @@
         <v>2.96</v>
       </c>
       <c r="G121" t="n">
-        <v>0.2609</v>
+        <v>26.087</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1739</v>
+        <v>17.3913</v>
       </c>
     </row>
   </sheetData>

--- a/demo/image_metadata_with_llava_long.xlsx
+++ b/demo/image_metadata_with_llava_long.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,16 @@
           <t>ROUGE-L_F</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>BERTScore</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>CLIPScore</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -491,6 +501,12 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
+      <c r="I2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>28.81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -525,6 +541,12 @@
       <c r="H3" t="n">
         <v>12.5</v>
       </c>
+      <c r="I3" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -559,6 +581,12 @@
       <c r="H4" t="n">
         <v>19.3548</v>
       </c>
+      <c r="I4" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -593,6 +621,12 @@
       <c r="H5" t="n">
         <v>11.2676</v>
       </c>
+      <c r="I5" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -627,6 +661,12 @@
       <c r="H6" t="n">
         <v>12.6984</v>
       </c>
+      <c r="I6" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -661,6 +701,12 @@
       <c r="H7" t="n">
         <v>14.8148</v>
       </c>
+      <c r="I7" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -695,6 +741,12 @@
       <c r="H8" t="n">
         <v>0</v>
       </c>
+      <c r="I8" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -729,6 +781,12 @@
       <c r="H9" t="n">
         <v>18.75</v>
       </c>
+      <c r="I9" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -763,6 +821,12 @@
       <c r="H10" t="n">
         <v>16</v>
       </c>
+      <c r="I10" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -797,6 +861,12 @@
       <c r="H11" t="n">
         <v>15</v>
       </c>
+      <c r="I11" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -831,6 +901,12 @@
       <c r="H12" t="n">
         <v>15.3846</v>
       </c>
+      <c r="I12" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -865,6 +941,12 @@
       <c r="H13" t="n">
         <v>20.339</v>
       </c>
+      <c r="I13" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -899,6 +981,12 @@
       <c r="H14" t="n">
         <v>7.1429</v>
       </c>
+      <c r="I14" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="J14" t="n">
+        <v>33.38</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -933,6 +1021,12 @@
       <c r="H15" t="n">
         <v>25</v>
       </c>
+      <c r="I15" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -967,6 +1061,12 @@
       <c r="H16" t="n">
         <v>20.6897</v>
       </c>
+      <c r="I16" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1001,6 +1101,12 @@
       <c r="H17" t="n">
         <v>28.5714</v>
       </c>
+      <c r="I17" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>35.21</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1035,6 +1141,12 @@
       <c r="H18" t="n">
         <v>8.1633</v>
       </c>
+      <c r="I18" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1069,6 +1181,12 @@
       <c r="H19" t="n">
         <v>15.0538</v>
       </c>
+      <c r="I19" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1103,6 +1221,12 @@
       <c r="H20" t="n">
         <v>0</v>
       </c>
+      <c r="I20" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1137,6 +1261,12 @@
       <c r="H21" t="n">
         <v>28.5714</v>
       </c>
+      <c r="I21" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1171,6 +1301,12 @@
       <c r="H22" t="n">
         <v>35.7143</v>
       </c>
+      <c r="I22" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1205,6 +1341,12 @@
       <c r="H23" t="n">
         <v>14.2857</v>
       </c>
+      <c r="I23" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1239,6 +1381,12 @@
       <c r="H24" t="n">
         <v>34.2857</v>
       </c>
+      <c r="I24" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1273,6 +1421,12 @@
       <c r="H25" t="n">
         <v>20</v>
       </c>
+      <c r="I25" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1307,6 +1461,12 @@
       <c r="H26" t="n">
         <v>31.8841</v>
       </c>
+      <c r="I26" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1341,6 +1501,12 @@
       <c r="H27" t="n">
         <v>7.4074</v>
       </c>
+      <c r="I27" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="J27" t="n">
+        <v>27.71</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1375,6 +1541,12 @@
       <c r="H28" t="n">
         <v>9.8361</v>
       </c>
+      <c r="I28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1409,6 +1581,12 @@
       <c r="H29" t="n">
         <v>8.6957</v>
       </c>
+      <c r="I29" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1443,6 +1621,12 @@
       <c r="H30" t="n">
         <v>8.6957</v>
       </c>
+      <c r="I30" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1477,6 +1661,12 @@
       <c r="H31" t="n">
         <v>19.2771</v>
       </c>
+      <c r="I31" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1511,6 +1701,12 @@
       <c r="H32" t="n">
         <v>15.3846</v>
       </c>
+      <c r="I32" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="J32" t="n">
+        <v>29.72</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1545,6 +1741,12 @@
       <c r="H33" t="n">
         <v>20.6897</v>
       </c>
+      <c r="I33" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1579,6 +1781,12 @@
       <c r="H34" t="n">
         <v>5.1282</v>
       </c>
+      <c r="I34" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1613,6 +1821,12 @@
       <c r="H35" t="n">
         <v>11.1111</v>
       </c>
+      <c r="I35" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1647,6 +1861,12 @@
       <c r="H36" t="n">
         <v>8.6957</v>
       </c>
+      <c r="I36" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1681,6 +1901,12 @@
       <c r="H37" t="n">
         <v>28.5714</v>
       </c>
+      <c r="I37" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="J37" t="n">
+        <v>31.72</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1715,6 +1941,12 @@
       <c r="H38" t="n">
         <v>23.5294</v>
       </c>
+      <c r="I38" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="J38" t="n">
+        <v>24.44</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1749,6 +1981,12 @@
       <c r="H39" t="n">
         <v>17.0213</v>
       </c>
+      <c r="I39" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1783,6 +2021,12 @@
       <c r="H40" t="n">
         <v>13.3333</v>
       </c>
+      <c r="I40" t="n">
+        <v>11</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1817,6 +2061,12 @@
       <c r="H41" t="n">
         <v>20</v>
       </c>
+      <c r="I41" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="J41" t="n">
+        <v>31.03</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1851,6 +2101,12 @@
       <c r="H42" t="n">
         <v>19.4444</v>
       </c>
+      <c r="I42" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1885,6 +2141,12 @@
       <c r="H43" t="n">
         <v>11.7647</v>
       </c>
+      <c r="I43" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1919,6 +2181,12 @@
       <c r="H44" t="n">
         <v>5.0633</v>
       </c>
+      <c r="I44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1953,6 +2221,12 @@
       <c r="H45" t="n">
         <v>5.8824</v>
       </c>
+      <c r="I45" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1987,6 +2261,12 @@
       <c r="H46" t="n">
         <v>5.5556</v>
       </c>
+      <c r="I46" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2021,6 +2301,12 @@
       <c r="H47" t="n">
         <v>15</v>
       </c>
+      <c r="I47" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2055,6 +2341,12 @@
       <c r="H48" t="n">
         <v>2.8986</v>
       </c>
+      <c r="I48" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2089,6 +2381,12 @@
       <c r="H49" t="n">
         <v>20</v>
       </c>
+      <c r="I49" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2123,6 +2421,12 @@
       <c r="H50" t="n">
         <v>8.333299999999999</v>
       </c>
+      <c r="I50" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2157,6 +2461,12 @@
       <c r="H51" t="n">
         <v>6.0606</v>
       </c>
+      <c r="I51" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2191,6 +2501,12 @@
       <c r="H52" t="n">
         <v>16.6667</v>
       </c>
+      <c r="I52" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2225,6 +2541,12 @@
       <c r="H53" t="n">
         <v>5</v>
       </c>
+      <c r="I53" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2259,6 +2581,12 @@
       <c r="H54" t="n">
         <v>15.625</v>
       </c>
+      <c r="I54" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2293,6 +2621,12 @@
       <c r="H55" t="n">
         <v>20.5128</v>
       </c>
+      <c r="I55" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2327,6 +2661,12 @@
       <c r="H56" t="n">
         <v>60</v>
       </c>
+      <c r="I56" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2361,6 +2701,12 @@
       <c r="H57" t="n">
         <v>20</v>
       </c>
+      <c r="I57" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2395,6 +2741,12 @@
       <c r="H58" t="n">
         <v>20.2899</v>
       </c>
+      <c r="I58" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2429,6 +2781,12 @@
       <c r="H59" t="n">
         <v>20</v>
       </c>
+      <c r="I59" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2463,6 +2821,12 @@
       <c r="H60" t="n">
         <v>15.3846</v>
       </c>
+      <c r="I60" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2497,6 +2861,12 @@
       <c r="H61" t="n">
         <v>3.125</v>
       </c>
+      <c r="I61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2531,6 +2901,12 @@
       <c r="H62" t="n">
         <v>0</v>
       </c>
+      <c r="I62" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="J62" t="n">
+        <v>29.89</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2565,6 +2941,12 @@
       <c r="H63" t="n">
         <v>5.5556</v>
       </c>
+      <c r="I63" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2599,6 +2981,12 @@
       <c r="H64" t="n">
         <v>7.6923</v>
       </c>
+      <c r="I64" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2633,6 +3021,12 @@
       <c r="H65" t="n">
         <v>6.8966</v>
       </c>
+      <c r="I65" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2667,6 +3061,12 @@
       <c r="H66" t="n">
         <v>0</v>
       </c>
+      <c r="I66" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2701,6 +3101,12 @@
       <c r="H67" t="n">
         <v>0</v>
       </c>
+      <c r="I67" t="n">
+        <v>-7.19</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2735,6 +3141,12 @@
       <c r="H68" t="n">
         <v>7.4074</v>
       </c>
+      <c r="I68" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2769,6 +3181,12 @@
       <c r="H69" t="n">
         <v>4.878</v>
       </c>
+      <c r="I69" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2803,6 +3221,12 @@
       <c r="H70" t="n">
         <v>0</v>
       </c>
+      <c r="I70" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2837,6 +3261,12 @@
       <c r="H71" t="n">
         <v>0</v>
       </c>
+      <c r="I71" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2871,6 +3301,12 @@
       <c r="H72" t="n">
         <v>20</v>
       </c>
+      <c r="I72" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2905,6 +3341,12 @@
       <c r="H73" t="n">
         <v>12</v>
       </c>
+      <c r="I73" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2939,6 +3381,12 @@
       <c r="H74" t="n">
         <v>11.1111</v>
       </c>
+      <c r="I74" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2973,6 +3421,12 @@
       <c r="H75" t="n">
         <v>8.6957</v>
       </c>
+      <c r="I75" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="J75" t="n">
+        <v>30.18</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3007,6 +3461,12 @@
       <c r="H76" t="n">
         <v>6.6667</v>
       </c>
+      <c r="I76" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3041,6 +3501,12 @@
       <c r="H77" t="n">
         <v>17.6471</v>
       </c>
+      <c r="I77" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3075,6 +3541,12 @@
       <c r="H78" t="n">
         <v>6.8966</v>
       </c>
+      <c r="I78" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3109,6 +3581,12 @@
       <c r="H79" t="n">
         <v>8.571400000000001</v>
       </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3143,6 +3621,12 @@
       <c r="H80" t="n">
         <v>8.6957</v>
       </c>
+      <c r="I80" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3177,6 +3661,12 @@
       <c r="H81" t="n">
         <v>16</v>
       </c>
+      <c r="I81" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3211,6 +3701,12 @@
       <c r="H82" t="n">
         <v>6.6667</v>
       </c>
+      <c r="I82" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3245,6 +3741,12 @@
       <c r="H83" t="n">
         <v>8.333299999999999</v>
       </c>
+      <c r="I83" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3279,6 +3781,12 @@
       <c r="H84" t="n">
         <v>17.3913</v>
       </c>
+      <c r="I84" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3313,6 +3821,12 @@
       <c r="H85" t="n">
         <v>22.8571</v>
       </c>
+      <c r="I85" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3347,6 +3861,12 @@
       <c r="H86" t="n">
         <v>7.6923</v>
       </c>
+      <c r="I86" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3381,6 +3901,12 @@
       <c r="H87" t="n">
         <v>21.7391</v>
       </c>
+      <c r="I87" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="J87" t="n">
+        <v>29.78</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3415,6 +3941,12 @@
       <c r="H88" t="n">
         <v>11.1111</v>
       </c>
+      <c r="I88" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3449,6 +3981,12 @@
       <c r="H89" t="n">
         <v>0</v>
       </c>
+      <c r="I89" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="J89" t="n">
+        <v>28.93</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3483,6 +4021,12 @@
       <c r="H90" t="n">
         <v>0</v>
       </c>
+      <c r="I90" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="J90" t="n">
+        <v>24.12</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3517,6 +4061,12 @@
       <c r="H91" t="n">
         <v>7.5472</v>
       </c>
+      <c r="I91" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="J91" t="n">
+        <v>28.81</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3551,6 +4101,12 @@
       <c r="H92" t="n">
         <v>14.6341</v>
       </c>
+      <c r="I92" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="J92" t="n">
+        <v>40.34</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3585,6 +4141,12 @@
       <c r="H93" t="n">
         <v>9.6774</v>
       </c>
+      <c r="I93" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3619,6 +4181,12 @@
       <c r="H94" t="n">
         <v>9.302300000000001</v>
       </c>
+      <c r="I94" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.37</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3653,6 +4221,12 @@
       <c r="H95" t="n">
         <v>6.7416</v>
       </c>
+      <c r="I95" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3687,6 +4261,12 @@
       <c r="H96" t="n">
         <v>9.0909</v>
       </c>
+      <c r="I96" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3721,6 +4301,12 @@
       <c r="H97" t="n">
         <v>16</v>
       </c>
+      <c r="I97" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3755,6 +4341,12 @@
       <c r="H98" t="n">
         <v>12.2449</v>
       </c>
+      <c r="I98" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3789,6 +4381,12 @@
       <c r="H99" t="n">
         <v>13.5593</v>
       </c>
+      <c r="I99" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3823,6 +4421,12 @@
       <c r="H100" t="n">
         <v>12.2449</v>
       </c>
+      <c r="I100" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3857,6 +4461,12 @@
       <c r="H101" t="n">
         <v>12.1212</v>
       </c>
+      <c r="I101" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3891,6 +4501,12 @@
       <c r="H102" t="n">
         <v>6.7797</v>
       </c>
+      <c r="I102" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3925,6 +4541,12 @@
       <c r="H103" t="n">
         <v>11.3636</v>
       </c>
+      <c r="I103" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3959,6 +4581,12 @@
       <c r="H104" t="n">
         <v>4.0816</v>
       </c>
+      <c r="I104" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3993,6 +4621,12 @@
       <c r="H105" t="n">
         <v>12.3077</v>
       </c>
+      <c r="I105" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4027,6 +4661,12 @@
       <c r="H106" t="n">
         <v>12.5</v>
       </c>
+      <c r="I106" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4061,6 +4701,12 @@
       <c r="H107" t="n">
         <v>15</v>
       </c>
+      <c r="I107" t="n">
+        <v>24</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4095,6 +4741,12 @@
       <c r="H108" t="n">
         <v>21.2766</v>
       </c>
+      <c r="I108" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4129,6 +4781,12 @@
       <c r="H109" t="n">
         <v>15.7895</v>
       </c>
+      <c r="I109" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4163,6 +4821,12 @@
       <c r="H110" t="n">
         <v>12</v>
       </c>
+      <c r="I110" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -4197,6 +4861,12 @@
       <c r="H111" t="n">
         <v>19.3548</v>
       </c>
+      <c r="I111" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4231,6 +4901,12 @@
       <c r="H112" t="n">
         <v>6.25</v>
       </c>
+      <c r="I112" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -4265,6 +4941,12 @@
       <c r="H113" t="n">
         <v>29.4118</v>
       </c>
+      <c r="I113" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -4299,6 +4981,12 @@
       <c r="H114" t="n">
         <v>14.4578</v>
       </c>
+      <c r="I114" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -4333,6 +5021,12 @@
       <c r="H115" t="n">
         <v>8.1633</v>
       </c>
+      <c r="I115" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4367,6 +5061,12 @@
       <c r="H116" t="n">
         <v>6.0606</v>
       </c>
+      <c r="I116" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4401,6 +5101,12 @@
       <c r="H117" t="n">
         <v>22.2222</v>
       </c>
+      <c r="I117" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4435,6 +5141,12 @@
       <c r="H118" t="n">
         <v>13.3333</v>
       </c>
+      <c r="I118" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4469,6 +5181,12 @@
       <c r="H119" t="n">
         <v>5.8824</v>
       </c>
+      <c r="I119" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4503,6 +5221,12 @@
       <c r="H120" t="n">
         <v>9.0909</v>
       </c>
+      <c r="I120" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4536,6 +5260,12 @@
       </c>
       <c r="H121" t="n">
         <v>17.3913</v>
+      </c>
+      <c r="I121" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="J121" t="n">
+        <v>28.14</v>
       </c>
     </row>
   </sheetData>
